--- a/data/trans_bre/P1432-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1432-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,22</t>
+          <t>-1,08; 3,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,73</t>
+          <t>0,32; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,97</t>
+          <t>-0,92; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1137,61</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,54</t>
+          <t>0,14; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,15</t>
+          <t>1,04; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,58</t>
+          <t>-0,47; 1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,14; —</t>
+          <t>-51,67; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,11; —</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,44</t>
+          <t>-1,26; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-76,31; 567,14</t>
+          <t>-77,85; 635,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,97</t>
+          <t>-1,23; 1,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,64</t>
+          <t>-0,34; 2,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,07</t>
+          <t>1,8; 6,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,05</t>
+          <t>-1,31; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>-2,22; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 889,38</t>
+          <t>-53,86; 1041,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,18</t>
+          <t>-0,65; 2,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,81</t>
+          <t>0,4; 3,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,84</t>
+          <t>-2,15; 1,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 364,45</t>
+          <t>-100,0; 347,86</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,61</t>
+          <t>-1,34; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,93</t>
+          <t>-1,92; 0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,37</t>
+          <t>0,75; 3,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,4</t>
+          <t>-91,93; 256,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-75,62; 117,94</t>
+          <t>-76,11; 128,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,06; 1888,38</t>
+          <t>29,59; 1665,59</t>
         </is>
       </c>
     </row>
@@ -1194,27 +1194,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,06</t>
+          <t>-1,53; 1,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,74</t>
+          <t>0,01; 1,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,19</t>
+          <t>-0,27; 1,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 128,79</t>
+          <t>-45,17; 106,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,56; —</t>
+          <t>-19,26; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,96</t>
+          <t>-0,19; 0,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,54</t>
+          <t>0,43; 1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,45</t>
+          <t>0,49; 1,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 112,56</t>
+          <t>-16,74; 103,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,2; 331,94</t>
+          <t>48,08; 338,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,3; 407,44</t>
+          <t>61,86; 371,26</t>
         </is>
       </c>
     </row>
